--- a/2022 data/excel_outputs/256_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/256_boothwise_data.xlsx
@@ -14,11 +14,95 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="517">
   <si>
     <t>AC 256 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
+    <t>Unnamed: 27</t>
+  </si>
+  <si>
+    <t>Unnamed: 28</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -646,7 +730,7 @@
     <t>PRATHMIK VIDYALAY HETAPATTI PASHCHIMI BHAG</t>
   </si>
   <si>
-    <t>PRATHMIK VIDYALAY HETAPATTI PURVI BHAG ■</t>
+    <t>IJ0 P0 A0 PA JHAMS U I PI(CHAMI BHAG</t>
   </si>
   <si>
     <t>PANCHAYAT BHAWAN BAHADURPUR TA0 IBRAHIMPUR PASHCHIMI BHAG</t>
@@ -1487,8 +1571,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1504,7 +1596,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1512,12 +1604,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1816,97 +1926,181 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:29">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>462</v>
+        <v>490</v>
       </c>
       <c r="D2" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="E2" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="F2" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="G2" t="s">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="H2" t="s">
-        <v>467</v>
+        <v>495</v>
       </c>
       <c r="I2" t="s">
-        <v>468</v>
+        <v>496</v>
       </c>
       <c r="J2" t="s">
-        <v>469</v>
+        <v>497</v>
       </c>
       <c r="K2" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="L2" t="s">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="M2" t="s">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="N2" t="s">
-        <v>473</v>
+        <v>501</v>
       </c>
       <c r="O2" t="s">
-        <v>474</v>
+        <v>502</v>
       </c>
       <c r="P2" t="s">
-        <v>475</v>
+        <v>503</v>
       </c>
       <c r="Q2" t="s">
-        <v>476</v>
+        <v>504</v>
       </c>
       <c r="R2" t="s">
-        <v>477</v>
+        <v>505</v>
       </c>
       <c r="S2" t="s">
-        <v>478</v>
+        <v>506</v>
       </c>
       <c r="T2" t="s">
-        <v>479</v>
+        <v>507</v>
       </c>
       <c r="U2" t="s">
-        <v>480</v>
+        <v>508</v>
       </c>
       <c r="V2" t="s">
-        <v>481</v>
+        <v>509</v>
       </c>
       <c r="W2" t="s">
-        <v>482</v>
+        <v>510</v>
       </c>
       <c r="X2" t="s">
-        <v>483</v>
+        <v>511</v>
       </c>
       <c r="Y2" t="s">
-        <v>484</v>
+        <v>512</v>
       </c>
       <c r="Z2" t="s">
-        <v>485</v>
+        <v>513</v>
       </c>
       <c r="AA2" t="s">
-        <v>486</v>
+        <v>514</v>
       </c>
       <c r="AB2" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="AC2" t="s">
-        <v>488</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -1914,7 +2108,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>884</v>
@@ -2003,7 +2197,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>1022</v>
@@ -2092,7 +2286,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>819</v>
@@ -2181,7 +2375,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>820</v>
@@ -2270,7 +2464,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>1019</v>
@@ -2359,7 +2553,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>630</v>
@@ -2448,7 +2642,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>704</v>
@@ -2537,7 +2731,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>1047</v>
@@ -2626,7 +2820,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <v>874</v>
@@ -2715,7 +2909,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>1064</v>
@@ -2804,7 +2998,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>1006</v>
@@ -2893,7 +3087,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>672</v>
@@ -2982,7 +3176,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C15">
         <v>707</v>
@@ -3071,7 +3265,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>1164</v>
@@ -3160,7 +3354,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C17">
         <v>1093</v>
@@ -3249,7 +3443,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <v>1159</v>
@@ -3338,7 +3532,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>974</v>
@@ -3427,7 +3621,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>749</v>
@@ -3516,7 +3710,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>992</v>
@@ -3605,7 +3799,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C22">
         <v>1191</v>
@@ -3694,7 +3888,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C23">
         <v>830</v>
@@ -3783,7 +3977,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C24">
         <v>669</v>
@@ -3872,7 +4066,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C25">
         <v>1031</v>
@@ -3961,7 +4155,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C26">
         <v>652</v>
@@ -4050,7 +4244,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C27">
         <v>454</v>
@@ -4139,7 +4333,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C28">
         <v>1129</v>
@@ -4228,7 +4422,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C29">
         <v>771</v>
@@ -4317,7 +4511,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C30">
         <v>792</v>
@@ -4406,7 +4600,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <v>1152</v>
@@ -4495,7 +4689,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C32">
         <v>1128</v>
@@ -4584,7 +4778,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C33">
         <v>840</v>
@@ -4673,7 +4867,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C34">
         <v>839</v>
@@ -4762,7 +4956,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C35">
         <v>815</v>
@@ -4851,7 +5045,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="C36">
         <v>490</v>
@@ -4940,7 +5134,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="C37">
         <v>1018</v>
@@ -5029,7 +5223,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="C38">
         <v>516</v>
@@ -5118,7 +5312,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="C39">
         <v>628</v>
@@ -5207,7 +5401,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C40">
         <v>843</v>
@@ -5296,7 +5490,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C41">
         <v>650</v>
@@ -5385,7 +5579,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C42">
         <v>1028</v>
@@ -5474,7 +5668,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C43">
         <v>1126</v>
@@ -5563,7 +5757,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C44">
         <v>838</v>
@@ -5652,7 +5846,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C45">
         <v>568</v>
@@ -5741,7 +5935,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="C46">
         <v>812</v>
@@ -5830,7 +6024,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C47">
         <v>795</v>
@@ -5919,7 +6113,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C48">
         <v>1108</v>
@@ -6008,7 +6202,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C49">
         <v>426</v>
@@ -6097,7 +6291,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C50">
         <v>933</v>
@@ -6186,7 +6380,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C51">
         <v>1037</v>
@@ -6275,7 +6469,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C52">
         <v>569</v>
@@ -6364,7 +6558,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C53">
         <v>795</v>
@@ -6453,7 +6647,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="C54">
         <v>957</v>
@@ -6542,7 +6736,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="C55">
         <v>659</v>
@@ -6631,7 +6825,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C56">
         <v>754</v>
@@ -6720,7 +6914,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C57">
         <v>751</v>
@@ -6809,7 +7003,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C58">
         <v>690</v>
@@ -6898,7 +7092,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="C59">
         <v>551</v>
@@ -6987,7 +7181,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="C60">
         <v>802</v>
@@ -7076,7 +7270,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="C61">
         <v>430</v>
@@ -7165,7 +7359,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="C62">
         <v>1031</v>
@@ -7254,7 +7448,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="C63">
         <v>794</v>
@@ -7343,7 +7537,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C64">
         <v>883</v>
@@ -7432,7 +7626,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="C65">
         <v>836</v>
@@ -7521,7 +7715,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C66">
         <v>625</v>
@@ -7610,7 +7804,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="C67">
         <v>1070</v>
@@ -7699,7 +7893,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="C68">
         <v>678</v>
@@ -7788,7 +7982,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C69">
         <v>782</v>
@@ -7877,7 +8071,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C70">
         <v>672</v>
@@ -7966,7 +8160,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C71">
         <v>592</v>
@@ -8055,7 +8249,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="C72">
         <v>1001</v>
@@ -8144,7 +8338,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C73">
         <v>875</v>
@@ -8233,7 +8427,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C74">
         <v>634</v>
@@ -8322,7 +8516,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="C75">
         <v>750</v>
@@ -8411,7 +8605,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="C76">
         <v>1096</v>
@@ -8500,7 +8694,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C77">
         <v>1134</v>
@@ -8589,7 +8783,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C78">
         <v>735</v>
@@ -8678,7 +8872,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C79">
         <v>1007</v>
@@ -8767,7 +8961,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="C80">
         <v>526</v>
@@ -8856,7 +9050,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C81">
         <v>998</v>
@@ -8945,7 +9139,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="C82">
         <v>1144</v>
@@ -9034,7 +9228,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C83">
         <v>985</v>
@@ -9123,7 +9317,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="C84">
         <v>296</v>
@@ -9212,7 +9406,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C85">
         <v>1094</v>
@@ -9301,7 +9495,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="C86">
         <v>1064</v>
@@ -9390,7 +9584,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="C87">
         <v>927</v>
@@ -9479,7 +9673,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C88">
         <v>662</v>
@@ -9568,7 +9762,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C89">
         <v>909</v>
@@ -9657,7 +9851,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="C90">
         <v>926</v>
@@ -9746,7 +9940,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="C91">
         <v>987</v>
@@ -9835,7 +10029,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C92">
         <v>559</v>
@@ -9924,7 +10118,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="C93">
         <v>1168</v>
@@ -10013,7 +10207,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="C94">
         <v>1118</v>
@@ -10102,7 +10296,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="C95">
         <v>1083</v>
@@ -10191,7 +10385,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="C96">
         <v>657</v>
@@ -10280,7 +10474,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="C97">
         <v>986</v>
@@ -10369,7 +10563,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="C98">
         <v>502</v>
@@ -10458,7 +10652,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="C99">
         <v>1126</v>
@@ -10547,7 +10741,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="C100">
         <v>599</v>
@@ -10636,7 +10830,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="C101">
         <v>724</v>
@@ -10725,7 +10919,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="C102">
         <v>805</v>
@@ -10814,7 +11008,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="C103">
         <v>773</v>
@@ -10903,7 +11097,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="C104">
         <v>945</v>
@@ -10992,7 +11186,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="C105">
         <v>1130</v>
@@ -11081,7 +11275,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="C106">
         <v>1061</v>
@@ -11170,7 +11364,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="C107">
         <v>948</v>
@@ -11259,7 +11453,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="C108">
         <v>1082</v>
@@ -11348,7 +11542,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="C109">
         <v>791</v>
@@ -11437,7 +11631,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="C110">
         <v>1010</v>
@@ -11526,7 +11720,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="C111">
         <v>730</v>
@@ -11615,7 +11809,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="C112">
         <v>844</v>
@@ -11704,7 +11898,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="C113">
         <v>455</v>
@@ -11793,7 +11987,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="C114">
         <v>1119</v>
@@ -11882,7 +12076,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="C115">
         <v>1126</v>
@@ -11971,7 +12165,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="C116">
         <v>1184</v>
@@ -12060,7 +12254,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="C117">
         <v>839</v>
@@ -12149,7 +12343,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="C118">
         <v>1082</v>
@@ -12238,7 +12432,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="C119">
         <v>997</v>
@@ -12327,7 +12521,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="C120">
         <v>1124</v>
@@ -12416,7 +12610,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="C121">
         <v>738</v>
@@ -12505,7 +12699,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="C122">
         <v>792</v>
@@ -12594,7 +12788,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="C123">
         <v>1044</v>
@@ -12683,7 +12877,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="C124">
         <v>819</v>
@@ -12772,7 +12966,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C125">
         <v>455</v>
@@ -12861,7 +13055,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C126">
         <v>880</v>
@@ -12950,7 +13144,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="C127">
         <v>811</v>
@@ -13039,7 +13233,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="C128">
         <v>988</v>
@@ -13128,7 +13322,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="C129">
         <v>852</v>
@@ -13217,7 +13411,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="C130">
         <v>1043</v>
@@ -13306,7 +13500,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="C131">
         <v>362</v>
@@ -13395,7 +13589,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="C132">
         <v>922</v>
@@ -13484,7 +13678,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="C133">
         <v>911</v>
@@ -13573,7 +13767,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="C134">
         <v>1098</v>
@@ -13662,7 +13856,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="C135">
         <v>991</v>
@@ -13751,7 +13945,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="C136">
         <v>1169</v>
@@ -13840,7 +14034,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="C137">
         <v>1092</v>
@@ -13929,7 +14123,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="C138">
         <v>1063</v>
@@ -14018,7 +14212,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="C139">
         <v>783</v>
@@ -14107,7 +14301,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="C140">
         <v>402</v>
@@ -14196,7 +14390,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="C141">
         <v>1077</v>
@@ -14285,7 +14479,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="C142">
         <v>557</v>
@@ -14374,7 +14568,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="C143">
         <v>817</v>
@@ -14463,7 +14657,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="C144">
         <v>659</v>
@@ -14552,7 +14746,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="C145">
         <v>941</v>
@@ -14641,7 +14835,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="C146">
         <v>722</v>
@@ -14730,7 +14924,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="C147">
         <v>735</v>
@@ -14819,7 +15013,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="C148">
         <v>835</v>
@@ -14908,7 +15102,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="C149">
         <v>690</v>
@@ -14997,7 +15191,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="C150">
         <v>696</v>
@@ -15086,7 +15280,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="C151">
         <v>1154</v>
@@ -15175,7 +15369,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="C152">
         <v>1001</v>
@@ -15264,7 +15458,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="C153">
         <v>1177</v>
@@ -15353,7 +15547,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="C154">
         <v>1086</v>
@@ -15442,7 +15636,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="C155">
         <v>628</v>
@@ -15531,7 +15725,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="C156">
         <v>1159</v>
@@ -15620,7 +15814,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="C157">
         <v>733</v>
@@ -15709,7 +15903,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="C158">
         <v>719</v>
@@ -15798,7 +15992,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="C159">
         <v>1014</v>
@@ -15887,7 +16081,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="C160">
         <v>859</v>
@@ -15976,7 +16170,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="C161">
         <v>864</v>
@@ -16065,7 +16259,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="C162">
         <v>881</v>
@@ -16154,7 +16348,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="C163">
         <v>824</v>
@@ -16243,7 +16437,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="C164">
         <v>662</v>
@@ -16332,7 +16526,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="C165">
         <v>1012</v>
@@ -16421,7 +16615,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="C166">
         <v>594</v>
@@ -16510,7 +16704,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="C167">
         <v>652</v>
@@ -16599,7 +16793,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="C168">
         <v>741</v>
@@ -16688,7 +16882,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="C169">
         <v>731</v>
@@ -16777,7 +16971,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="C170">
         <v>517</v>
@@ -16866,7 +17060,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="C171">
         <v>636</v>
@@ -16955,7 +17149,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C172">
         <v>1136</v>
@@ -17044,7 +17238,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="C173">
         <v>810</v>
@@ -17133,7 +17327,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="C174">
         <v>1102</v>
@@ -17222,7 +17416,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="C175">
         <v>1009</v>
@@ -17311,7 +17505,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="C176">
         <v>1090</v>
@@ -17400,7 +17594,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="C177">
         <v>1183</v>
@@ -17489,7 +17683,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="C178">
         <v>605</v>
@@ -17578,7 +17772,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="C179">
         <v>616</v>
@@ -17667,7 +17861,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="C180">
         <v>902</v>
@@ -17756,7 +17950,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="C181">
         <v>668</v>
@@ -17845,7 +18039,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="C182">
         <v>896</v>
@@ -17934,7 +18128,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="C183">
         <v>710</v>
@@ -18023,7 +18217,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C184">
         <v>496</v>
@@ -18112,7 +18306,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="C185">
         <v>655</v>
@@ -18201,7 +18395,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="C186">
         <v>943</v>
@@ -18290,7 +18484,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="C187">
         <v>1019</v>
@@ -18379,7 +18573,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C188">
         <v>1001</v>
@@ -18468,7 +18662,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C189">
         <v>819</v>
@@ -18557,7 +18751,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="C190">
         <v>1098</v>
@@ -18646,7 +18840,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="C191">
         <v>1174</v>
@@ -18735,7 +18929,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="C192">
         <v>593</v>
@@ -18824,7 +19018,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="C193">
         <v>639</v>
@@ -18913,7 +19107,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="C194">
         <v>810</v>
@@ -19002,7 +19196,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="C195">
         <v>511</v>
@@ -19091,7 +19285,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="C196">
         <v>600</v>
@@ -19180,7 +19374,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="C197">
         <v>724</v>
@@ -19269,7 +19463,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="C198">
         <v>938</v>
@@ -19358,7 +19552,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="C199">
         <v>932</v>
@@ -19447,7 +19641,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="C200">
         <v>731</v>
@@ -19536,7 +19730,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="C201">
         <v>845</v>
@@ -19625,7 +19819,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="C202">
         <v>895</v>
@@ -19714,7 +19908,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="C203">
         <v>834</v>
@@ -19803,7 +19997,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="C204">
         <v>531</v>
@@ -19892,7 +20086,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C205">
         <v>1108</v>
@@ -19981,7 +20175,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>1170</v>
@@ -20070,7 +20264,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="C207">
         <v>893</v>
@@ -20159,7 +20353,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="C208">
         <v>712</v>
@@ -20248,7 +20442,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="C209">
         <v>1070</v>
@@ -20337,7 +20531,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="C210">
         <v>778</v>
@@ -20426,7 +20620,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="C211">
         <v>631</v>
@@ -20515,7 +20709,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C212">
         <v>778</v>
@@ -20604,7 +20798,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="C213">
         <v>721</v>
@@ -20693,7 +20887,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="C214">
         <v>584</v>
@@ -20782,7 +20976,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="C215">
         <v>1151</v>
@@ -20871,7 +21065,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="C216">
         <v>980</v>
@@ -20960,7 +21154,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="C217">
         <v>715</v>
@@ -21049,7 +21243,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="C218">
         <v>689</v>
@@ -21138,7 +21332,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="C219">
         <v>615</v>
@@ -21227,7 +21421,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="C220">
         <v>679</v>
@@ -21316,7 +21510,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="C221">
         <v>929</v>
@@ -21405,7 +21599,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="C222">
         <v>1004</v>
@@ -21494,7 +21688,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="C223">
         <v>843</v>
@@ -21583,7 +21777,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="C224">
         <v>788</v>
@@ -21672,7 +21866,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="C225">
         <v>693</v>
@@ -21761,7 +21955,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="C226">
         <v>631</v>
@@ -21850,7 +22044,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="C227">
         <v>619</v>
@@ -21939,7 +22133,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="C228">
         <v>756</v>
@@ -22028,7 +22222,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="C229">
         <v>760</v>
@@ -22117,7 +22311,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="C230">
         <v>710</v>
@@ -22206,7 +22400,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="C231">
         <v>756</v>
@@ -22295,7 +22489,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="C232">
         <v>1076</v>
@@ -22384,7 +22578,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="C233">
         <v>938</v>
@@ -22473,7 +22667,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="C234">
         <v>1097</v>
@@ -22562,7 +22756,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="C235">
         <v>1167</v>
@@ -22651,7 +22845,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="C236">
         <v>763</v>
@@ -22740,7 +22934,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="C237">
         <v>525</v>
@@ -22829,7 +23023,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="C238">
         <v>730</v>
@@ -22918,7 +23112,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="C239">
         <v>927</v>
@@ -23007,7 +23201,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="C240">
         <v>472</v>
@@ -23096,7 +23290,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="C241">
         <v>693</v>
@@ -23185,7 +23379,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="C242">
         <v>912</v>
@@ -23274,7 +23468,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="C243">
         <v>1097</v>
@@ -23363,7 +23557,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="C244">
         <v>1113</v>
@@ -23452,7 +23646,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="C245">
         <v>970</v>
@@ -23541,7 +23735,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="C246">
         <v>1029</v>
@@ -23630,7 +23824,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="C247">
         <v>762</v>
@@ -23719,7 +23913,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>245</v>
+        <v>273</v>
       </c>
       <c r="C248">
         <v>491</v>
@@ -23808,7 +24002,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="C249">
         <v>1153</v>
@@ -23897,7 +24091,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="C250">
         <v>1052</v>
@@ -23986,7 +24180,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="C251">
         <v>1027</v>
@@ -24075,7 +24269,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="C252">
         <v>930</v>
@@ -24164,7 +24358,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="C253">
         <v>743</v>
@@ -24253,7 +24447,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="C254">
         <v>1176</v>
@@ -24342,7 +24536,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="C255">
         <v>1095</v>
@@ -24431,7 +24625,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="C256">
         <v>1170</v>
@@ -24520,7 +24714,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="C257">
         <v>1131</v>
@@ -24609,7 +24803,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="C258">
         <v>1116</v>
@@ -24698,7 +24892,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="C259">
         <v>816</v>
@@ -24787,7 +24981,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>257</v>
+        <v>285</v>
       </c>
       <c r="C260">
         <v>1042</v>
@@ -24876,7 +25070,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="C261">
         <v>973</v>
@@ -24965,7 +25159,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>259</v>
+        <v>287</v>
       </c>
       <c r="C262">
         <v>1183</v>
@@ -25054,7 +25248,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="C263">
         <v>1105</v>
@@ -25143,7 +25337,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="C264">
         <v>1116</v>
@@ -25232,7 +25426,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>262</v>
+        <v>290</v>
       </c>
       <c r="C265">
         <v>1037</v>
@@ -25321,7 +25515,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>263</v>
+        <v>291</v>
       </c>
       <c r="C266">
         <v>655</v>
@@ -25410,7 +25604,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="C267">
         <v>1184</v>
@@ -25499,7 +25693,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="C268">
         <v>1196</v>
@@ -25588,7 +25782,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="C269">
         <v>1194</v>
@@ -25677,7 +25871,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="C270">
         <v>951</v>
@@ -25766,7 +25960,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="C271">
         <v>1082</v>
@@ -25855,7 +26049,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="C272">
         <v>1166</v>
@@ -25944,7 +26138,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="C273">
         <v>1132</v>
@@ -26033,7 +26227,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="C274">
         <v>995</v>
@@ -26122,7 +26316,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="C275">
         <v>1050</v>
@@ -26211,7 +26405,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="C276">
         <v>1009</v>
@@ -26300,7 +26494,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="C277">
         <v>1041</v>
@@ -26389,7 +26583,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="C278">
         <v>1158</v>
@@ -26478,7 +26672,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="C279">
         <v>1029</v>
@@ -26567,7 +26761,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="C280">
         <v>938</v>
@@ -26656,7 +26850,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="C281">
         <v>954</v>
@@ -26745,7 +26939,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="C282">
         <v>1065</v>
@@ -26834,7 +27028,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="C283">
         <v>1087</v>
@@ -26923,7 +27117,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="C284">
         <v>1083</v>
@@ -27012,7 +27206,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="C285">
         <v>1185</v>
@@ -27101,7 +27295,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
       <c r="C286">
         <v>1145</v>
@@ -27190,7 +27384,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>284</v>
+        <v>312</v>
       </c>
       <c r="C287">
         <v>846</v>
@@ -27279,7 +27473,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>285</v>
+        <v>313</v>
       </c>
       <c r="C288">
         <v>876</v>
@@ -27368,7 +27562,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="C289">
         <v>1165</v>
@@ -27457,7 +27651,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="C290">
         <v>1161</v>
@@ -27546,7 +27740,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="C291">
         <v>773</v>
@@ -27635,7 +27829,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="C292">
         <v>665</v>
@@ -27724,7 +27918,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="C293">
         <v>1041</v>
@@ -27813,7 +28007,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>291</v>
+        <v>319</v>
       </c>
       <c r="C294">
         <v>911</v>
@@ -27902,7 +28096,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="C295">
         <v>1033</v>
@@ -27991,7 +28185,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="C296">
         <v>1088</v>
@@ -28080,7 +28274,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="C297">
         <v>1103</v>
@@ -28169,7 +28363,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="C298">
         <v>1040</v>
@@ -28258,7 +28452,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="C299">
         <v>1178</v>
@@ -28347,7 +28541,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
       <c r="C300">
         <v>833</v>
@@ -28436,7 +28630,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="C301">
         <v>977</v>
@@ -28525,7 +28719,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C302">
         <v>1191</v>
@@ -28614,7 +28808,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>300</v>
+        <v>328</v>
       </c>
       <c r="C303">
         <v>1190</v>
@@ -28703,7 +28897,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="C304">
         <v>1062</v>
@@ -28792,7 +28986,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="C305">
         <v>1134</v>
@@ -28881,7 +29075,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="C306">
         <v>1100</v>
@@ -28970,7 +29164,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>304</v>
+        <v>332</v>
       </c>
       <c r="C307">
         <v>863</v>
@@ -29059,7 +29253,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>305</v>
+        <v>333</v>
       </c>
       <c r="C308">
         <v>947</v>
@@ -29148,7 +29342,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="C309">
         <v>803</v>
@@ -29237,7 +29431,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
       <c r="C310">
         <v>840</v>
@@ -29326,7 +29520,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="C311">
         <v>1150</v>
@@ -29415,7 +29609,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
       <c r="C312">
         <v>729</v>
@@ -29504,7 +29698,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="C313">
         <v>1022</v>
@@ -29593,7 +29787,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="C314">
         <v>915</v>
@@ -29682,7 +29876,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>312</v>
+        <v>340</v>
       </c>
       <c r="C315">
         <v>614</v>
@@ -29771,7 +29965,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="C316">
         <v>631</v>
@@ -29860,7 +30054,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="C317">
         <v>1184</v>
@@ -29949,7 +30143,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="C318">
         <v>756</v>
@@ -30038,7 +30232,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="C319">
         <v>809</v>
@@ -30127,7 +30321,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
       <c r="C320">
         <v>1117</v>
@@ -30216,7 +30410,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>318</v>
+        <v>346</v>
       </c>
       <c r="C321">
         <v>1102</v>
@@ -30305,7 +30499,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="C322">
         <v>804</v>
@@ -30394,7 +30588,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="C323">
         <v>837</v>
@@ -30483,7 +30677,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="C324">
         <v>1177</v>
@@ -30572,7 +30766,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="C325">
         <v>1061</v>
@@ -30661,7 +30855,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="C326">
         <v>719</v>
@@ -30750,7 +30944,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="C327">
         <v>624</v>
@@ -30839,7 +31033,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="C328">
         <v>1111</v>
@@ -30928,7 +31122,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="C329">
         <v>1090</v>
@@ -31017,7 +31211,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="C330">
         <v>1034</v>
@@ -31106,7 +31300,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="C331">
         <v>1017</v>
@@ -31195,7 +31389,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="C332">
         <v>987</v>
@@ -31284,7 +31478,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="C333">
         <v>1052</v>
@@ -31373,7 +31567,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="C334">
         <v>811</v>
@@ -31462,7 +31656,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="C335">
         <v>566</v>
@@ -31551,7 +31745,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="C336">
         <v>1026</v>
@@ -31640,7 +31834,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="C337">
         <v>619</v>
@@ -31729,7 +31923,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
       <c r="C338">
         <v>972</v>
@@ -31818,7 +32012,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="C339">
         <v>1068</v>
@@ -31907,7 +32101,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="C340">
         <v>1159</v>
@@ -31996,7 +32190,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="C341">
         <v>688</v>
@@ -32085,7 +32279,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="C342">
         <v>677</v>
@@ -32174,7 +32368,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="C343">
         <v>683</v>
@@ -32263,7 +32457,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="C344">
         <v>733</v>
@@ -32352,7 +32546,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="C345">
         <v>806</v>
@@ -32441,7 +32635,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="C346">
         <v>750</v>
@@ -32530,7 +32724,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="C347">
         <v>1139</v>
@@ -32619,7 +32813,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="C348">
         <v>755</v>
@@ -32708,7 +32902,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="C349">
         <v>680</v>
@@ -32797,7 +32991,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="C350">
         <v>686</v>
@@ -32886,7 +33080,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="C351">
         <v>859</v>
@@ -32975,7 +33169,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="C352">
         <v>892</v>
@@ -33064,7 +33258,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="C353">
         <v>975</v>
@@ -33153,7 +33347,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="C354">
         <v>815</v>
@@ -33242,7 +33436,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="C355">
         <v>925</v>
@@ -33331,7 +33525,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="C356">
         <v>766</v>
@@ -33420,7 +33614,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="C357">
         <v>733</v>
@@ -33509,7 +33703,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="C358">
         <v>1125</v>
@@ -33598,7 +33792,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="C359">
         <v>1076</v>
@@ -33687,7 +33881,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="C360">
         <v>1001</v>
@@ -33776,7 +33970,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="C361">
         <v>1063</v>
@@ -33865,7 +34059,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="C362">
         <v>866</v>
@@ -33954,7 +34148,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="C363">
         <v>795</v>
@@ -34043,7 +34237,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="C364">
         <v>1198</v>
@@ -34132,7 +34326,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="C365">
         <v>959</v>
@@ -34221,7 +34415,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="C366">
         <v>1129</v>
@@ -34310,7 +34504,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="C367">
         <v>656</v>
@@ -34399,7 +34593,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="C368">
         <v>630</v>
@@ -34488,7 +34682,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C369">
         <v>693</v>
@@ -34577,7 +34771,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="C370">
         <v>1084</v>
@@ -34666,7 +34860,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="C371">
         <v>647</v>
@@ -34755,7 +34949,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="C372">
         <v>620</v>
@@ -34844,7 +35038,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="C373">
         <v>1110</v>
@@ -34933,7 +35127,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="C374">
         <v>619</v>
@@ -35022,7 +35216,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="C375">
         <v>629</v>
@@ -35111,7 +35305,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="C376">
         <v>778</v>
@@ -35200,7 +35394,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="C377">
         <v>1006</v>
@@ -35289,7 +35483,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="C378">
         <v>1030</v>
@@ -35378,7 +35572,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="C379">
         <v>707</v>
@@ -35467,7 +35661,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="C380">
         <v>867</v>
@@ -35556,7 +35750,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="C381">
         <v>600</v>
@@ -35645,7 +35839,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="C382">
         <v>605</v>
@@ -35734,7 +35928,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="C383">
         <v>994</v>
@@ -35823,7 +36017,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="C384">
         <v>1093</v>
@@ -35912,7 +36106,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="C385">
         <v>1154</v>
@@ -36001,7 +36195,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="C386">
         <v>1014</v>
@@ -36090,7 +36284,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="C387">
         <v>500</v>
@@ -36179,7 +36373,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="C388">
         <v>1015</v>
@@ -36268,7 +36462,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="C389">
         <v>1095</v>
@@ -36357,7 +36551,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="C390">
         <v>1011</v>
@@ -36446,7 +36640,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="C391">
         <v>838</v>
@@ -36535,7 +36729,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="C392">
         <v>1034</v>
@@ -36624,7 +36818,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="C393">
         <v>1067</v>
@@ -36713,7 +36907,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="C394">
         <v>662</v>
@@ -36802,7 +36996,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="C395">
         <v>806</v>
@@ -36891,7 +37085,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="C396">
         <v>1056</v>
@@ -36980,7 +37174,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="C397">
         <v>846</v>
@@ -37069,7 +37263,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="C398">
         <v>995</v>
@@ -37158,7 +37352,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="C399">
         <v>983</v>
@@ -37247,7 +37441,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="C400">
         <v>610</v>
@@ -37336,7 +37530,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="C401">
         <v>624</v>
@@ -37425,7 +37619,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="C402">
         <v>1179</v>
@@ -37514,7 +37708,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="C403">
         <v>663</v>
@@ -37603,7 +37797,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="C404">
         <v>849</v>
@@ -37692,7 +37886,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="C405">
         <v>1028</v>
@@ -37781,7 +37975,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="C406">
         <v>687</v>
@@ -37870,7 +38064,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="C407">
         <v>744</v>
@@ -37959,7 +38153,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="C408">
         <v>824</v>
@@ -38048,7 +38242,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="C409">
         <v>645</v>
@@ -38137,7 +38331,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="C410">
         <v>623</v>
@@ -38226,7 +38420,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="C411">
         <v>1010</v>
@@ -38315,7 +38509,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="C412">
         <v>1097</v>
@@ -38404,7 +38598,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="C413">
         <v>927</v>
@@ -38493,7 +38687,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="C414">
         <v>1009</v>
@@ -38582,7 +38776,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="C415">
         <v>1040</v>
@@ -38671,7 +38865,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="C416">
         <v>652</v>
@@ -38760,7 +38954,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="C417">
         <v>785</v>
@@ -38849,7 +39043,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="C418">
         <v>1036</v>
@@ -38938,7 +39132,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="C419">
         <v>475</v>
@@ -39027,7 +39221,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="C420">
         <v>1115</v>
@@ -39116,7 +39310,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="C421">
         <v>1207</v>
@@ -39205,7 +39399,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="C422">
         <v>1059</v>
@@ -39294,7 +39488,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="C423">
         <v>1060</v>
@@ -39383,7 +39577,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="C424">
         <v>1168</v>
@@ -39472,7 +39666,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="C425">
         <v>929</v>
@@ -39561,7 +39755,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="C426">
         <v>691</v>
@@ -39650,7 +39844,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="C427">
         <v>874</v>
@@ -39739,7 +39933,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="C428">
         <v>960</v>
@@ -39828,7 +40022,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="C429">
         <v>644</v>
@@ -39917,7 +40111,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="C430">
         <v>605</v>
@@ -40006,7 +40200,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="C431">
         <v>970</v>
@@ -40095,7 +40289,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="C432">
         <v>1113</v>
@@ -40184,7 +40378,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="C433">
         <v>799</v>
@@ -40273,7 +40467,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="C434">
         <v>615</v>
@@ -40362,7 +40556,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="C435">
         <v>867</v>
@@ -40451,7 +40645,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="C436">
         <v>918</v>
@@ -40540,7 +40734,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="C437">
         <v>854</v>
@@ -40629,7 +40823,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="C438">
         <v>896</v>
@@ -40718,7 +40912,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="C439">
         <v>868</v>
@@ -40807,7 +41001,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="C440">
         <v>1074</v>
@@ -40896,7 +41090,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="C441">
         <v>702</v>
@@ -40985,7 +41179,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="C442">
         <v>1007</v>
@@ -41074,7 +41268,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="C443">
         <v>988</v>
@@ -41163,7 +41357,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="C444">
         <v>409</v>
@@ -41252,7 +41446,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="C445">
         <v>991</v>
@@ -41341,7 +41535,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="C446">
         <v>566</v>
@@ -41430,7 +41624,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="C447">
         <v>718</v>
@@ -41519,7 +41713,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="C448">
         <v>777</v>
@@ -41608,7 +41802,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="C449">
         <v>841</v>
@@ -41697,7 +41891,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="C450">
         <v>1102</v>
@@ -41786,7 +41980,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="C451">
         <v>803</v>
@@ -41875,7 +42069,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="C452">
         <v>691</v>
@@ -41964,7 +42158,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="C453">
         <v>852</v>
@@ -42053,7 +42247,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="C454">
         <v>750</v>
@@ -42142,7 +42336,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="C455">
         <v>867</v>
@@ -42231,7 +42425,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="C456">
         <v>671</v>
@@ -42320,7 +42514,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="C457">
         <v>702</v>
@@ -42409,7 +42603,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="C458">
         <v>790</v>
@@ -42498,7 +42692,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="C459">
         <v>554</v>
@@ -42587,7 +42781,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="C460">
         <v>442</v>
@@ -42676,7 +42870,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="C461">
         <v>1130</v>
@@ -42765,7 +42959,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="C462">
         <v>685</v>
@@ -42854,7 +43048,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="C463">
         <v>1180</v>
@@ -42943,7 +43137,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="C464">
         <v>1026</v>
@@ -43032,7 +43226,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>461</v>
+        <v>489</v>
       </c>
       <c r="C465">
         <v>1117</v>
